--- a/mallar/Protokoll/Protokoll_2019_lag_sv-r_mellan(mall)_mer_an_6_deltagar.xlsx
+++ b/mallar/Protokoll/Protokoll_2019_lag_sv-r_mellan(mall)_mer_an_6_deltagar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\episerver\voltige\VoltigeClosedXML\mallar\Protokoll\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\episerver\voltige\VoltigeClosedXML\voltexc\mallar\Protokoll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A9E596-1FE1-4FF6-8AE5-529AC0425079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081C53EE-22A0-46D8-929E-A5D70279844F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="81480" yWindow="-120" windowWidth="29040" windowHeight="17640" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54495" yWindow="0" windowWidth="26010" windowHeight="20985" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Information" sheetId="27" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <definedName name="datum" localSheetId="5">'Lag kür tekn mellan'!$C$4</definedName>
     <definedName name="datum" localSheetId="7">'Lag kür tekn sr'!$C$4</definedName>
     <definedName name="domare" localSheetId="1">'Häst_old, lag'!$C$31</definedName>
-    <definedName name="domare" localSheetId="2">'Lag grund A'!$C$33</definedName>
+    <definedName name="domare" localSheetId="2">'Lag grund A'!$C$32</definedName>
     <definedName name="domare" localSheetId="3">'Lag grund B'!$C$32</definedName>
     <definedName name="domare" localSheetId="4">'Lag grund D'!$C$33</definedName>
     <definedName name="domare" localSheetId="8">'Lag kür art'!$C$29</definedName>
@@ -89,7 +89,7 @@
     <definedName name="moment" localSheetId="5">'Lag kür tekn mellan'!$L$5</definedName>
     <definedName name="moment" localSheetId="7">'Lag kür tekn sr'!$L$5</definedName>
     <definedName name="result" localSheetId="1">'Häst_old, lag'!$J$27</definedName>
-    <definedName name="result" localSheetId="2">'Lag grund A'!$O$29</definedName>
+    <definedName name="result" localSheetId="2">'Lag grund A'!$O$28</definedName>
     <definedName name="result" localSheetId="3">'Lag grund B'!$O$29</definedName>
     <definedName name="result" localSheetId="4">'Lag grund D'!$O$29</definedName>
     <definedName name="result" localSheetId="8">'Lag kür art'!$L$26</definedName>
@@ -113,7 +113,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="168">
   <si>
     <t>1)</t>
   </si>
@@ -337,9 +337,6 @@
     <t>Avdrag för fall</t>
   </si>
   <si>
-    <t>Sidhopp del 1</t>
-  </si>
-  <si>
     <t>Teknisk bedömning</t>
   </si>
   <si>
@@ -548,9 +545,6 @@
   </si>
   <si>
     <t>Sving baklänges, inkl avgång</t>
-  </si>
-  <si>
-    <t>Avhopp, utåt</t>
   </si>
   <si>
     <t>Lag grund D</t>
@@ -787,6 +781,9 @@
   <si>
     <t>C4
 25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/ 7 övningar  </t>
   </si>
 </sst>
 </file>
@@ -1655,7 +1652,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="254">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2108,34 +2105,157 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="16" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="32" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="3" fillId="3" borderId="19" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2151,86 +2271,17 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="41" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="40" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="49" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="50" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="37" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="25" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="justify" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2252,18 +2303,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
@@ -2297,46 +2336,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2656,109 +2662,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q60"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="18" width="15.73046875" customWidth="1"/>
+    <col min="1" max="18" width="15.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="148" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:8" s="148" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="147" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="148" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="148" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="148" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="148" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" s="148" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="148" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="163" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="163" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="163" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="163" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="163" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="163" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="163" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:8" s="134" customFormat="1" ht="17.25" x14ac:dyDescent="0.45">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="163" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:8" s="148" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:8" s="134" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A8" s="134" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="135"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="135"/>
+    </row>
+    <row r="12" spans="1:8" s="136" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="136" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="135"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="135"/>
-    </row>
-    <row r="12" spans="1:8" s="136" customFormat="1" ht="13.15" x14ac:dyDescent="0.4">
-      <c r="A12" s="136" t="s">
+    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="137" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="137" t="s">
-        <v>96</v>
       </c>
       <c r="C13" s="135"/>
       <c r="F13" s="137" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="136" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="136" t="s">
+      <c r="C14" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="136" t="s">
+      <c r="D14" s="136" t="s">
         <v>99</v>
-      </c>
-      <c r="D14" s="136" t="s">
-        <v>100</v>
       </c>
       <c r="E14" s="136"/>
       <c r="F14" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="G14" s="136" t="s">
+      <c r="H14" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="H14" s="136" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="135" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B15" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D15" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E15" s="139"/>
       <c r="F15" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G15" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H15" s="138" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="135"/>
       <c r="B16" s="140"/>
       <c r="C16" s="140"/>
@@ -2768,31 +2774,31 @@
       <c r="G16" s="140"/>
       <c r="H16" s="140"/>
     </row>
-    <row r="17" spans="1:9" s="135" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" s="135" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="135" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B17" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C17" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D17" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E17" s="139"/>
       <c r="F17" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G17" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H17" s="138" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="135"/>
       <c r="B18" s="140"/>
       <c r="C18" s="140"/>
@@ -2802,31 +2808,31 @@
       <c r="G18" s="140"/>
       <c r="H18" s="140"/>
     </row>
-    <row r="19" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="135" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B19" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C19" s="138" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D19" s="138" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E19" s="139"/>
       <c r="F19" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" s="138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H19" s="138" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="135"/>
       <c r="B20" s="141"/>
       <c r="C20" s="141"/>
@@ -2836,76 +2842,76 @@
       <c r="G20" s="141"/>
       <c r="H20" s="141"/>
     </row>
-    <row r="22" spans="1:9" s="136" customFormat="1" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:9" s="136" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A22" s="136" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C23" s="135"/>
       <c r="F23" s="137" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="136" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="136" t="s">
+      <c r="C24" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="C24" s="136" t="s">
+      <c r="D24" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="D24" s="136" t="s">
-        <v>100</v>
-      </c>
       <c r="E24" s="136" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F24" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="G24" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="G24" s="136" t="s">
+      <c r="H24" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="H24" s="136" t="s">
-        <v>100</v>
-      </c>
       <c r="I24" s="136" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="135" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C25" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D25" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E25" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F25" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G25" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H25" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I25" s="138" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="135"/>
       <c r="B26" s="140"/>
       <c r="C26" s="140"/>
@@ -2916,36 +2922,36 @@
       <c r="H26" s="140"/>
       <c r="I26" s="140"/>
     </row>
-    <row r="27" spans="1:9" s="135" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" s="135" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="135" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C27" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D27" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E27" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F27" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G27" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H27" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I27" s="138" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="135"/>
       <c r="B28" s="140"/>
       <c r="C28" s="140"/>
@@ -2956,134 +2962,134 @@
       <c r="H28" s="140"/>
       <c r="I28" s="140"/>
     </row>
-    <row r="29" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="135" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="138" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="138" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="H29" s="138" t="s">
         <v>108</v>
       </c>
-      <c r="B29" s="138" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="F29" s="138" t="s">
-        <v>105</v>
-      </c>
-      <c r="G29" s="138" t="s">
-        <v>129</v>
-      </c>
-      <c r="H29" s="138" t="s">
-        <v>109</v>
-      </c>
       <c r="I29" s="138" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="162"/>
       <c r="C30" s="162"/>
       <c r="D30" s="162"/>
       <c r="E30" s="162"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="162"/>
       <c r="C31" s="162"/>
       <c r="D31" s="162"/>
       <c r="E31" s="162"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B32" s="162"/>
       <c r="C32" s="162"/>
       <c r="D32" s="162"/>
       <c r="E32" s="162"/>
     </row>
-    <row r="33" spans="1:17" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" ht="13" x14ac:dyDescent="0.3">
       <c r="A33" s="136" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" s="135"/>
       <c r="F35" s="137" t="s">
+        <v>96</v>
+      </c>
+      <c r="J35" s="137" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="136" t="s">
         <v>97</v>
       </c>
-      <c r="J35" s="137" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="136" t="s">
+      <c r="C36" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="136" t="s">
+      <c r="D36" s="136" t="s">
         <v>99</v>
-      </c>
-      <c r="D36" s="136" t="s">
-        <v>100</v>
       </c>
       <c r="E36" s="136"/>
       <c r="F36" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="136" t="s">
+      <c r="H36" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="H36" s="136" t="s">
-        <v>100</v>
-      </c>
       <c r="J36" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="K36" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="K36" s="136" t="s">
+      <c r="L36" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="L36" s="136" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="135" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B37" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C37" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D37" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E37" s="139"/>
       <c r="F37" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G37" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H37" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J37" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K37" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L37" s="138" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="135"/>
       <c r="B38" s="140"/>
       <c r="C38" s="140"/>
@@ -3096,40 +3102,40 @@
       <c r="K38" s="140"/>
       <c r="L38" s="140"/>
     </row>
-    <row r="39" spans="1:17" s="135" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" s="135" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="135" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B39" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C39" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D39" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E39" s="139"/>
       <c r="F39" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H39" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J39" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K39" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L39" s="138" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="135"/>
       <c r="B40" s="140"/>
       <c r="C40" s="140"/>
@@ -3142,40 +3148,40 @@
       <c r="K40" s="140"/>
       <c r="L40" s="140"/>
     </row>
-    <row r="41" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="135" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B41" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C41" s="138" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D41" s="138" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E41" s="139"/>
       <c r="F41" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G41" s="138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H41" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J41" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K41" s="138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L41" s="138" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="135"/>
       <c r="B42" s="162"/>
       <c r="C42" s="162"/>
@@ -3188,7 +3194,7 @@
       <c r="K42" s="162"/>
       <c r="L42" s="162"/>
     </row>
-    <row r="43" spans="1:17" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="135"/>
       <c r="B43" s="162"/>
       <c r="C43" s="162"/>
@@ -3201,109 +3207,109 @@
       <c r="K43" s="162"/>
       <c r="L43" s="162"/>
     </row>
-    <row r="45" spans="1:17" ht="13.15" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" ht="13" x14ac:dyDescent="0.3">
       <c r="A45" s="136" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="137" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="135"/>
       <c r="F47" s="137" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J47" s="137" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K47" s="135"/>
       <c r="N47" s="137"/>
     </row>
-    <row r="48" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="136" t="s">
+      <c r="D48" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="136" t="s">
-        <v>100</v>
-      </c>
       <c r="E48" s="136" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F48" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="G48" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="G48" s="136" t="s">
+      <c r="H48" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="H48" s="136" t="s">
-        <v>100</v>
-      </c>
       <c r="I48" s="136" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J48" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="K48" s="136" t="s">
         <v>98</v>
       </c>
-      <c r="K48" s="136" t="s">
+      <c r="L48" s="136" t="s">
         <v>99</v>
       </c>
-      <c r="L48" s="136" t="s">
-        <v>100</v>
-      </c>
       <c r="M48" s="136" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N48" s="136"/>
       <c r="O48" s="136"/>
       <c r="P48" s="136"/>
       <c r="Q48" s="136"/>
     </row>
-    <row r="49" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="135" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B49" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C49" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D49" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E49" s="138" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F49" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G49" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H49" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I49" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="J49" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K49" s="138" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L49" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M49" s="138" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="135"/>
       <c r="B50" s="140"/>
       <c r="C50" s="140"/>
@@ -3318,48 +3324,48 @@
       <c r="L50" s="140"/>
       <c r="M50" s="140"/>
     </row>
-    <row r="51" spans="1:13" s="135" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" s="135" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="135" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B51" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C51" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D51" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E51" s="138" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F51" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G51" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="H51" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I51" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="J51" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K51" s="138" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L51" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M51" s="138" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="135"/>
       <c r="B52" s="140"/>
       <c r="C52" s="140"/>
@@ -3374,118 +3380,118 @@
       <c r="L52" s="140"/>
       <c r="M52" s="140"/>
     </row>
-    <row r="53" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="135" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53" s="138" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="E53" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="F53" s="138" t="s">
+        <v>104</v>
+      </c>
+      <c r="G53" s="138" t="s">
+        <v>128</v>
+      </c>
+      <c r="H53" s="138" t="s">
         <v>108</v>
       </c>
-      <c r="B53" s="138" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="D53" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="E53" s="138" t="s">
-        <v>138</v>
-      </c>
-      <c r="F53" s="138" t="s">
-        <v>105</v>
-      </c>
-      <c r="G53" s="138" t="s">
-        <v>129</v>
-      </c>
-      <c r="H53" s="138" t="s">
-        <v>109</v>
-      </c>
       <c r="I53" s="138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J53" s="138" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K53" s="138" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L53" s="138" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M53" s="138" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" s="148" customFormat="1" ht="17.25" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" s="148" customFormat="1" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A56" s="146" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" s="145" customFormat="1" ht="13.15" x14ac:dyDescent="0.4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" s="145" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="A57" s="144"/>
       <c r="B57" s="144" t="s">
+        <v>97</v>
+      </c>
+      <c r="C57" s="144" t="s">
         <v>98</v>
       </c>
-      <c r="C57" s="144" t="s">
+      <c r="D57" s="144" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="144" t="s">
-        <v>100</v>
-      </c>
       <c r="E57" s="144" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F57" s="144" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" s="143" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="142" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="58" spans="1:13" s="143" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="142" t="s">
+      <c r="B58" s="142" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="142" t="s">
+      <c r="C58" s="142" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="142" t="s">
+      <c r="D58" s="142" t="s">
+        <v>117</v>
+      </c>
+      <c r="E58" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="D58" s="142" t="s">
-        <v>118</v>
-      </c>
-      <c r="E58" s="142" t="s">
+      <c r="F58" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="F58" s="142" t="s">
+    </row>
+    <row r="59" spans="1:13" s="143" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="142" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="59" spans="1:13" s="143" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="142" t="s">
+      <c r="B59" s="142" t="s">
+        <v>116</v>
+      </c>
+      <c r="C59" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="B59" s="142" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="142" t="s">
+      <c r="D59" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="D59" s="142" t="s">
+      <c r="E59" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="E59" s="142" t="s">
-        <v>124</v>
-      </c>
       <c r="F59" s="142" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" s="143" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" s="143" customFormat="1" ht="25" x14ac:dyDescent="0.25">
       <c r="A60" s="142"/>
       <c r="B60" s="142"/>
       <c r="C60" s="142"/>
       <c r="D60" s="142"/>
       <c r="E60" s="142"/>
       <c r="F60" s="142" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3506,30 +3512,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.86328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.73046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -3537,11 +3543,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -3558,7 +3564,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -3594,9 +3600,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -3606,29 +3612,29 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="175"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="177"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="177"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="179"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I8" s="174"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="181"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="176"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -3641,13 +3647,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="174"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="181"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="176"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -3658,53 +3664,53 @@
         <v>3</v>
       </c>
       <c r="I10" s="174"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="181"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="176"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I11" s="174"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="181"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="176"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I12" s="174"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="180"/>
-      <c r="L12" s="181"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
+      <c r="L12" s="176"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="14"/>
       <c r="H13" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I13" s="174"/>
       <c r="J13" s="174"/>
       <c r="K13" s="174"/>
       <c r="L13" s="174"/>
     </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="14"/>
       <c r="H14" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I14" s="174"/>
       <c r="J14" s="174"/>
       <c r="K14" s="174"/>
       <c r="L14" s="174"/>
     </row>
-    <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="14"/>
       <c r="H15" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I15" s="174"/>
       <c r="J15" s="174"/>
@@ -3713,25 +3719,25 @@
     </row>
     <row r="16" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K16" s="164" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="171" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="190" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="191"/>
+      <c r="D17" s="191"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="191"/>
+      <c r="H17" s="191"/>
+      <c r="I17" s="192"/>
+      <c r="J17" s="168" t="s">
         <v>153</v>
-      </c>
-      <c r="B17" s="240" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="241"/>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="168" t="s">
-        <v>155</v>
       </c>
       <c r="K17" s="172"/>
       <c r="L17" s="173">
@@ -3740,21 +3746,21 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="243" t="s">
-        <v>164</v>
-      </c>
-      <c r="B18" s="246" t="s">
+      <c r="A18" s="180" t="s">
         <v>162</v>
       </c>
-      <c r="C18" s="247"/>
-      <c r="D18" s="247"/>
-      <c r="E18" s="247"/>
-      <c r="F18" s="247"/>
-      <c r="G18" s="247"/>
-      <c r="H18" s="247"/>
-      <c r="I18" s="247"/>
+      <c r="B18" s="182" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="183"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="183"/>
+      <c r="I18" s="183"/>
       <c r="J18" s="100" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K18" s="156"/>
       <c r="L18" s="101">
@@ -3764,19 +3770,19 @@
       <c r="M18" s="102"/>
     </row>
     <row r="19" spans="1:13" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="244"/>
-      <c r="B19" s="246" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="247"/>
-      <c r="D19" s="247"/>
-      <c r="E19" s="247"/>
-      <c r="F19" s="247"/>
-      <c r="G19" s="247"/>
-      <c r="H19" s="247"/>
-      <c r="I19" s="247"/>
+      <c r="A19" s="193"/>
+      <c r="B19" s="182" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="183"/>
+      <c r="I19" s="183"/>
       <c r="J19" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K19" s="157"/>
       <c r="L19" s="104">
@@ -3786,21 +3792,21 @@
       <c r="M19" s="102"/>
     </row>
     <row r="20" spans="1:13" ht="58.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="243" t="s">
-        <v>165</v>
-      </c>
-      <c r="B20" s="248" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="249"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="249"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="249"/>
-      <c r="H20" s="249"/>
-      <c r="I20" s="250"/>
+      <c r="A20" s="180" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="184" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="185"/>
+      <c r="F20" s="185"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
+      <c r="I20" s="186"/>
       <c r="J20" s="100" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K20" s="158"/>
       <c r="L20" s="105">
@@ -3810,19 +3816,19 @@
       <c r="M20" s="102"/>
     </row>
     <row r="21" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="245"/>
-      <c r="B21" s="251" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="252"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
-      <c r="I21" s="253"/>
+      <c r="A21" s="181"/>
+      <c r="B21" s="187" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="188"/>
+      <c r="D21" s="188"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="188"/>
+      <c r="I21" s="189"/>
       <c r="J21" s="106" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K21" s="159"/>
       <c r="L21" s="107">
@@ -3845,7 +3851,7 @@
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="83"/>
       <c r="D24" s="70"/>
@@ -3861,9 +3867,9 @@
     <row r="25" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L25" s="90"/>
     </row>
-    <row r="26" spans="1:13" ht="13.9" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I26" s="71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J26" s="98"/>
       <c r="K26" s="98"/>
@@ -3890,11 +3896,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="I8:L8"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
@@ -3904,13 +3912,11 @@
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="I13:L13"/>
     <mergeCell ref="I14:L14"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B19:I19"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3926,31 +3932,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="43" customWidth="1"/>
-    <col min="2" max="2" width="10.265625" style="43" customWidth="1"/>
-    <col min="3" max="3" width="12.59765625" style="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.73046875" style="43" customWidth="1"/>
-    <col min="5" max="5" width="7.265625" style="43" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" style="43" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="43" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" style="43" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" style="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.7265625" style="43" customWidth="1"/>
+    <col min="5" max="5" width="7.26953125" style="43" customWidth="1"/>
+    <col min="6" max="6" width="14.6328125" style="43" customWidth="1"/>
     <col min="7" max="7" width="7" style="43" customWidth="1"/>
-    <col min="8" max="8" width="9.59765625" style="43" customWidth="1"/>
-    <col min="9" max="9" width="5.73046875" style="43" customWidth="1"/>
-    <col min="10" max="10" width="5.59765625" style="43" customWidth="1"/>
-    <col min="11" max="11" width="7.1328125" style="43" customWidth="1"/>
-    <col min="12" max="12" width="7.265625" style="43" customWidth="1"/>
-    <col min="13" max="16384" width="9.1328125" style="43"/>
+    <col min="8" max="8" width="9.6328125" style="43" customWidth="1"/>
+    <col min="9" max="9" width="5.7265625" style="43" customWidth="1"/>
+    <col min="10" max="10" width="5.6328125" style="43" customWidth="1"/>
+    <col min="11" max="11" width="7.08984375" style="43" customWidth="1"/>
+    <col min="12" max="12" width="7.26953125" style="43" customWidth="1"/>
+    <col min="13" max="16384" width="9.08984375" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" s="1" customFormat="1" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I2" s="10"/>
       <c r="J2" s="11"/>
@@ -3962,7 +3968,7 @@
       </c>
       <c r="G3" s="9"/>
       <c r="H3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I3" s="10"/>
       <c r="J3" s="11"/>
@@ -3978,7 +3984,7 @@
       <c r="E4" s="8"/>
       <c r="G4" s="9"/>
       <c r="H4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I4" s="10"/>
       <c r="J4" s="11"/>
@@ -4012,9 +4018,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" s="1" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -4023,28 +4029,28 @@
       <c r="G7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="175"/>
-      <c r="I7" s="176"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="177"/>
-    </row>
-    <row r="8" spans="1:11" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H7" s="177"/>
+      <c r="I7" s="178"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="179"/>
+    </row>
+    <row r="8" spans="1:11" s="1" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
       <c r="G8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="H8" s="174"/>
-      <c r="I8" s="180"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="181"/>
-    </row>
-    <row r="9" spans="1:11" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="175"/>
+      <c r="J8" s="175"/>
+      <c r="K8" s="176"/>
+    </row>
+    <row r="9" spans="1:11" s="1" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -4056,13 +4062,13 @@
         <v>2</v>
       </c>
       <c r="H9" s="174"/>
-      <c r="I9" s="180"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="181"/>
-    </row>
-    <row r="10" spans="1:11" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I9" s="175"/>
+      <c r="J9" s="175"/>
+      <c r="K9" s="176"/>
+    </row>
+    <row r="10" spans="1:11" s="1" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -4072,28 +4078,28 @@
         <v>3</v>
       </c>
       <c r="H10" s="174"/>
-      <c r="I10" s="180"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="181"/>
-    </row>
-    <row r="11" spans="1:11" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="175"/>
+      <c r="J10" s="175"/>
+      <c r="K10" s="176"/>
+    </row>
+    <row r="11" spans="1:11" s="1" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G11" s="12" t="s">
         <v>4</v>
       </c>
       <c r="H11" s="174"/>
-      <c r="I11" s="180"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="181"/>
-    </row>
-    <row r="12" spans="1:11" s="1" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="175"/>
+      <c r="J11" s="175"/>
+      <c r="K11" s="176"/>
+    </row>
+    <row r="12" spans="1:11" s="1" customFormat="1" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="G12" s="12" t="s">
         <v>5</v>
       </c>
       <c r="H12" s="174"/>
-      <c r="I12" s="180"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="181"/>
+      <c r="I12" s="175"/>
+      <c r="J12" s="175"/>
+      <c r="K12" s="176"/>
     </row>
     <row r="13" spans="1:11" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="14"/>
@@ -4104,205 +4110,205 @@
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G14" s="192" t="s">
+      <c r="G14" s="219" t="s">
         <v>54</v>
       </c>
-      <c r="H14" s="193"/>
-      <c r="I14" s="194" t="s">
-        <v>87</v>
-      </c>
-      <c r="J14" s="195"/>
-      <c r="K14" s="196"/>
+      <c r="H14" s="220"/>
+      <c r="I14" s="221" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="222"/>
+      <c r="K14" s="223"/>
     </row>
     <row r="15" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="197" t="s">
+      <c r="A15" s="196" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="200" t="s">
+      <c r="B15" s="210" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="200" t="s">
+      <c r="C15" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="200"/>
-      <c r="E15" s="201" t="s">
+      <c r="D15" s="210"/>
+      <c r="E15" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="202"/>
+      <c r="F15" s="214"/>
       <c r="G15" s="44"/>
       <c r="H15" s="45"/>
-      <c r="I15" s="203" t="s">
+      <c r="I15" s="202" t="s">
         <v>7</v>
       </c>
-      <c r="J15" s="187"/>
-      <c r="K15" s="182">
+      <c r="J15" s="228"/>
+      <c r="K15" s="226">
         <f>ROUND(J15*0.3,3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="198"/>
-      <c r="B16" s="184"/>
-      <c r="C16" s="184" t="s">
+      <c r="A16" s="197"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="184"/>
-      <c r="E16" s="185" t="s">
+      <c r="D16" s="204"/>
+      <c r="E16" s="205" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="186"/>
+      <c r="F16" s="206"/>
       <c r="G16" s="46"/>
       <c r="H16" s="47"/>
-      <c r="I16" s="204"/>
-      <c r="J16" s="188"/>
-      <c r="K16" s="183"/>
+      <c r="I16" s="203"/>
+      <c r="J16" s="229"/>
+      <c r="K16" s="227"/>
     </row>
     <row r="17" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="198"/>
-      <c r="B17" s="184"/>
-      <c r="C17" s="184" t="s">
+      <c r="A17" s="197"/>
+      <c r="B17" s="204"/>
+      <c r="C17" s="204" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="184"/>
-      <c r="E17" s="185" t="s">
+      <c r="D17" s="204"/>
+      <c r="E17" s="205" t="s">
         <v>45</v>
       </c>
-      <c r="F17" s="186"/>
+      <c r="F17" s="206"/>
       <c r="G17" s="48"/>
       <c r="H17" s="49"/>
-      <c r="I17" s="204"/>
-      <c r="J17" s="188"/>
-      <c r="K17" s="183"/>
+      <c r="I17" s="203"/>
+      <c r="J17" s="229"/>
+      <c r="K17" s="227"/>
     </row>
     <row r="18" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="198"/>
-      <c r="B18" s="205" t="s">
+      <c r="A18" s="197"/>
+      <c r="B18" s="215" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="184" t="s">
+      <c r="C18" s="204" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="184"/>
-      <c r="E18" s="185" t="s">
+      <c r="D18" s="204"/>
+      <c r="E18" s="205" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="186"/>
+      <c r="F18" s="206"/>
       <c r="G18" s="50"/>
       <c r="H18" s="51"/>
-      <c r="I18" s="204" t="s">
+      <c r="I18" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="188"/>
-      <c r="K18" s="183">
+      <c r="J18" s="229"/>
+      <c r="K18" s="227">
         <f>ROUND(J18*0.25,3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="198"/>
-      <c r="B19" s="206"/>
-      <c r="C19" s="184" t="s">
+      <c r="A19" s="197"/>
+      <c r="B19" s="216"/>
+      <c r="C19" s="204" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="184"/>
-      <c r="E19" s="185" t="s">
+      <c r="D19" s="204"/>
+      <c r="E19" s="205" t="s">
         <v>42</v>
       </c>
-      <c r="F19" s="186"/>
+      <c r="F19" s="206"/>
       <c r="G19" s="46"/>
       <c r="H19" s="47"/>
-      <c r="I19" s="204"/>
-      <c r="J19" s="188"/>
-      <c r="K19" s="183"/>
+      <c r="I19" s="203"/>
+      <c r="J19" s="229"/>
+      <c r="K19" s="227"/>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="199"/>
-      <c r="B20" s="207"/>
-      <c r="C20" s="209" t="s">
+      <c r="A20" s="198"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="207" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="209"/>
-      <c r="E20" s="210" t="s">
+      <c r="D20" s="207"/>
+      <c r="E20" s="208" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="211"/>
+      <c r="F20" s="209"/>
       <c r="G20" s="52"/>
       <c r="H20" s="53"/>
-      <c r="I20" s="208"/>
-      <c r="J20" s="189"/>
-      <c r="K20" s="190"/>
+      <c r="I20" s="218"/>
+      <c r="J20" s="230"/>
+      <c r="K20" s="231"/>
     </row>
     <row r="21" spans="1:11" ht="47.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="197" t="s">
+      <c r="A21" s="196" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="214" t="s">
+      <c r="B21" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="200" t="s">
+      <c r="C21" s="210" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="200"/>
-      <c r="E21" s="217" t="s">
+      <c r="D21" s="210"/>
+      <c r="E21" s="211" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="218"/>
+      <c r="F21" s="212"/>
       <c r="G21" s="54"/>
       <c r="H21" s="55"/>
-      <c r="I21" s="203" t="s">
-        <v>91</v>
-      </c>
-      <c r="J21" s="187"/>
-      <c r="K21" s="182">
+      <c r="I21" s="202" t="s">
+        <v>90</v>
+      </c>
+      <c r="J21" s="228"/>
+      <c r="K21" s="226">
         <f>ROUND(J21*0.25,3)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="198"/>
-      <c r="B22" s="215"/>
-      <c r="C22" s="184" t="s">
+      <c r="A22" s="197"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="D22" s="184"/>
-      <c r="E22" s="185" t="s">
+      <c r="D22" s="204"/>
+      <c r="E22" s="205" t="s">
         <v>39</v>
       </c>
-      <c r="F22" s="186"/>
+      <c r="F22" s="206"/>
       <c r="G22" s="46"/>
       <c r="H22" s="47"/>
-      <c r="I22" s="204"/>
-      <c r="J22" s="188"/>
-      <c r="K22" s="183"/>
+      <c r="I22" s="203"/>
+      <c r="J22" s="229"/>
+      <c r="K22" s="227"/>
     </row>
     <row r="23" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="198"/>
-      <c r="B23" s="216"/>
-      <c r="C23" s="184" t="s">
+      <c r="A23" s="197"/>
+      <c r="B23" s="201"/>
+      <c r="C23" s="204" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="184"/>
-      <c r="E23" s="185" t="s">
+      <c r="D23" s="204"/>
+      <c r="E23" s="205" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="186"/>
+      <c r="F23" s="206"/>
       <c r="G23" s="48"/>
       <c r="H23" s="49"/>
-      <c r="I23" s="204"/>
-      <c r="J23" s="188"/>
-      <c r="K23" s="183"/>
+      <c r="I23" s="203"/>
+      <c r="J23" s="229"/>
+      <c r="K23" s="227"/>
     </row>
     <row r="24" spans="1:11" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="199"/>
+      <c r="A24" s="198"/>
       <c r="B24" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="209"/>
-      <c r="D24" s="209"/>
-      <c r="E24" s="210" t="s">
+      <c r="C24" s="207"/>
+      <c r="D24" s="207"/>
+      <c r="E24" s="208" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="211"/>
+      <c r="F24" s="209"/>
       <c r="G24" s="57"/>
       <c r="H24" s="58"/>
       <c r="I24" s="59" t="s">
@@ -4319,20 +4325,20 @@
         <v>35</v>
       </c>
       <c r="B25" s="133" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="191" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25" s="232" t="s">
         <v>29</v>
       </c>
-      <c r="D25" s="191"/>
-      <c r="E25" s="212" t="s">
+      <c r="D25" s="232"/>
+      <c r="E25" s="194" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="213"/>
+      <c r="F25" s="195"/>
       <c r="G25" s="61"/>
       <c r="H25" s="62"/>
       <c r="I25" s="63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J25" s="152"/>
       <c r="K25" s="64">
@@ -4340,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" ht="9.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="65"/>
       <c r="B26" s="65"/>
       <c r="C26" s="65"/>
@@ -4353,7 +4359,7 @@
       <c r="J26" s="65"/>
       <c r="K26" s="65"/>
     </row>
-    <row r="27" spans="1:11" ht="16.350000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" ht="16.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="65"/>
       <c r="B27" s="65"/>
       <c r="C27" s="65"/>
@@ -4365,13 +4371,13 @@
         <v>11</v>
       </c>
       <c r="I27" s="67"/>
-      <c r="J27" s="178">
+      <c r="J27" s="224">
         <f>SUM(K15:K25)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="179"/>
-    </row>
-    <row r="31" spans="1:11" ht="12.75" x14ac:dyDescent="0.35">
+      <c r="K27" s="225"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
         <v>31</v>
       </c>
@@ -4390,40 +4396,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="B15:B17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="I15:I17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="I18:I20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="H10:K10"/>
     <mergeCell ref="C5:E5"/>
     <mergeCell ref="H7:K7"/>
     <mergeCell ref="C6:E6"/>
@@ -4440,6 +4412,40 @@
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="J21:J23"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="H8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="I15:I17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4458,34 +4464,34 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V35"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V34"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="11" width="7.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.1328125" style="1"/>
-    <col min="15" max="15" width="14.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="11" width="7.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" style="1"/>
+    <col min="15" max="15" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="R2" s="9"/>
       <c r="S2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T2" s="10"/>
       <c r="U2" s="11"/>
@@ -4493,7 +4499,7 @@
     </row>
     <row r="3" spans="1:22" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J3" s="165" t="str">
         <f>IF(L3&lt;&gt;0,J2+1,"0")</f>
@@ -4502,13 +4508,13 @@
       <c r="K3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="175"/>
-      <c r="M3" s="175"/>
-      <c r="N3" s="175"/>
-      <c r="O3" s="228"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="233"/>
       <c r="R3" s="9"/>
       <c r="S3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T3" s="10"/>
       <c r="U3" s="11"/>
@@ -4533,10 +4539,10 @@
       <c r="L4" s="174"/>
       <c r="M4" s="174"/>
       <c r="N4" s="174"/>
-      <c r="O4" s="229"/>
+      <c r="O4" s="234"/>
       <c r="R4" s="9"/>
       <c r="S4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T4" s="10"/>
       <c r="U4" s="11"/>
@@ -4559,9 +4565,9 @@
         <v>2</v>
       </c>
       <c r="L5" s="174"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="181"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="176"/>
       <c r="R5" s="9"/>
       <c r="S5" s="13" t="s">
         <v>12</v>
@@ -4587,13 +4593,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="174"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="180"/>
-      <c r="O6" s="181"/>
-    </row>
-    <row r="7" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="175"/>
+      <c r="N6" s="175"/>
+      <c r="O6" s="176"/>
+    </row>
+    <row r="7" spans="1:22" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -4608,19 +4614,19 @@
         <v>4</v>
       </c>
       <c r="L7" s="174"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="181"/>
-    </row>
-    <row r="8" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="175"/>
+      <c r="N7" s="175"/>
+      <c r="O7" s="176"/>
+    </row>
+    <row r="8" spans="1:22" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="J8" s="165" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4629,11 +4635,11 @@
         <v>5</v>
       </c>
       <c r="L8" s="174"/>
-      <c r="M8" s="180"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="181"/>
-    </row>
-    <row r="9" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="175"/>
+      <c r="N8" s="175"/>
+      <c r="O8" s="176"/>
+    </row>
+    <row r="9" spans="1:22" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -4647,16 +4653,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L9" s="174"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="180"/>
-      <c r="O9" s="181"/>
-    </row>
-    <row r="10" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="175"/>
+      <c r="N9" s="175"/>
+      <c r="O9" s="176"/>
+    </row>
+    <row r="10" spans="1:22" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -4668,27 +4674,27 @@
         <v>0</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L10" s="174"/>
-      <c r="M10" s="180"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="181"/>
-    </row>
-    <row r="11" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="175"/>
+      <c r="N10" s="175"/>
+      <c r="O10" s="176"/>
+    </row>
+    <row r="11" spans="1:22" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J11" s="165" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L11" s="174"/>
-      <c r="M11" s="180"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="181"/>
-    </row>
-    <row r="12" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="M11" s="175"/>
+      <c r="N11" s="175"/>
+      <c r="O11" s="176"/>
+    </row>
+    <row r="12" spans="1:22" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:22" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
       <c r="B13" s="16"/>
@@ -4725,13 +4731,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="219"/>
-      <c r="B15" s="220" t="s">
+    <row r="15" spans="1:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="237"/>
+      <c r="B15" s="238" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="221"/>
-      <c r="D15" s="221"/>
+      <c r="C15" s="239"/>
+      <c r="D15" s="239"/>
       <c r="E15" s="18"/>
       <c r="F15" s="153"/>
       <c r="G15" s="153"/>
@@ -4749,13 +4755,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="219"/>
-      <c r="B16" s="222" t="s">
+    <row r="16" spans="1:22" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="237"/>
+      <c r="B16" s="240" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="239"/>
       <c r="E16" s="18"/>
       <c r="F16" s="153"/>
       <c r="G16" s="153"/>
@@ -4769,16 +4775,16 @@
         <v>0</v>
       </c>
       <c r="O16" s="19">
-        <f t="shared" ref="O16:O22" si="1">SUM(F16:N16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="222" t="s">
+        <f t="shared" ref="O16:O21" si="1">SUM(F16:N16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="240" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="221"/>
-      <c r="D17" s="221"/>
+      <c r="C17" s="239"/>
+      <c r="D17" s="239"/>
       <c r="E17" s="18"/>
       <c r="F17" s="153"/>
       <c r="G17" s="153"/>
@@ -4796,12 +4802,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="226" t="s">
+    <row r="18" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="235" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="227"/>
-      <c r="D18" s="227"/>
+      <c r="C18" s="236"/>
+      <c r="D18" s="236"/>
       <c r="E18" s="18"/>
       <c r="F18" s="153"/>
       <c r="G18" s="153"/>
@@ -4819,12 +4825,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="222" t="s">
+    <row r="19" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="240" t="s">
         <v>61</v>
       </c>
-      <c r="C19" s="221"/>
-      <c r="D19" s="221"/>
+      <c r="C19" s="239"/>
+      <c r="D19" s="239"/>
       <c r="E19" s="20"/>
       <c r="F19" s="153"/>
       <c r="G19" s="153"/>
@@ -4842,7 +4848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="69" t="s">
         <v>52</v>
       </c>
@@ -4865,13 +4871,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="69" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" s="70"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="18"/>
+    <row r="21" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="254" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="255"/>
+      <c r="D21" s="255"/>
+      <c r="E21" s="256"/>
       <c r="F21" s="153"/>
       <c r="G21" s="153"/>
       <c r="H21" s="153"/>
@@ -4888,148 +4894,137 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="223" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="224"/>
-      <c r="D22" s="224"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="153"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="153"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="153"/>
-      <c r="L22" s="153"/>
-      <c r="M22" s="153"/>
-      <c r="N22" s="153">
-        <v>0</v>
-      </c>
-      <c r="O22" s="19">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M23" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="O23" s="1">
+    <row r="22" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M22" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O22" s="1">
         <f>MAX(J3:J11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="22" t="s">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="23"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="23"/>
+      <c r="N23" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="O23" s="19">
+        <f>SUM(O15:O21)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="25"/>
+      <c r="H24" s="26"/>
+      <c r="M24" s="24"/>
       <c r="N24" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="O24" s="19">
-        <f>SUM(O15:O22)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>146</v>
+      </c>
+      <c r="O24" s="27">
+        <f>IFERROR(ROUND(O23/O22,3),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B25" s="25"/>
       <c r="H25" s="26"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="O25" s="27">
-        <f>IFERROR(ROUND(O24/O23,3),0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B26" s="25"/>
-      <c r="H26" s="26"/>
-      <c r="M26" s="29"/>
-      <c r="O26" s="30"/>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.3">
-      <c r="B27" s="31"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="32"/>
-      <c r="L27" s="28"/>
-      <c r="N27" s="24" t="s">
-        <v>62</v>
-      </c>
-      <c r="O27" s="29"/>
-    </row>
-    <row r="28" spans="2:15" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="29" spans="2:15" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="M25" s="29"/>
+      <c r="O25" s="30"/>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B26" s="31"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="32"/>
+      <c r="L26" s="28"/>
+      <c r="N26" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="O26" s="29"/>
+    </row>
+    <row r="27" spans="1:15" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="1:15" ht="23.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F28" s="38"/>
+      <c r="H28" s="33"/>
+      <c r="L28" s="71" t="s">
+        <v>63</v>
+      </c>
+      <c r="M28" s="72"/>
+      <c r="N28" s="73"/>
+      <c r="O28" s="37">
+        <f>ROUND(+O24/7,3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="38"/>
       <c r="H29" s="33"/>
-      <c r="L29" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="M29" s="72"/>
-      <c r="N29" s="73"/>
-      <c r="O29" s="37">
-        <f>ROUND(+O25/8,3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="33"/>
+      <c r="J29" s="39"/>
+      <c r="K29" s="24"/>
+    </row>
+    <row r="30" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F30" s="38"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="J30" s="39"/>
       <c r="K30" s="24"/>
-    </row>
-    <row r="31" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F31" s="38"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="24"/>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="38"/>
+      <c r="H32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+    </row>
     <row r="33" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
-      <c r="E33" s="40"/>
       <c r="F33" s="38"/>
-      <c r="H33" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F34" s="38"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="39"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C6:F6"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="L9:O9"/>
@@ -5039,25 +5034,13 @@
     <mergeCell ref="L5:O5"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="L7:O7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B19:D19"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddHeader>&amp;L&amp;G
 &amp;C&amp;"Verdana,Normal"&amp;12PROTOKOLL FÖR LAGTÄVLAN</oddHeader>
-    <oddFooter xml:space="preserve">&amp;R2020-01-06
+    <oddFooter xml:space="preserve">&amp;R2026-03-22
 </oddFooter>
   </headerFooter>
   <legacyDrawingHF r:id="rId2"/>
@@ -5070,33 +5053,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T34"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="11" width="7.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.1328125" style="1"/>
-    <col min="15" max="15" width="12.73046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="11" width="7.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" style="1"/>
+    <col min="15" max="15" width="12.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:20" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:20" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R2" s="10"/>
       <c r="S2" s="11"/>
@@ -5104,7 +5087,7 @@
     </row>
     <row r="3" spans="1:20" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J3" s="165" t="str">
         <f>IF(L3&lt;&gt;0,I2+1,"0")</f>
@@ -5119,7 +5102,7 @@
       <c r="O3" s="166"/>
       <c r="P3" s="9"/>
       <c r="Q3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R3" s="10"/>
       <c r="S3" s="11"/>
@@ -5147,7 +5130,7 @@
       <c r="O4" s="167"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R4" s="10"/>
       <c r="S4" s="11"/>
@@ -5202,9 +5185,9 @@
       <c r="N6" s="12"/>
       <c r="O6" s="130"/>
     </row>
-    <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -5223,15 +5206,15 @@
       <c r="N7" s="12"/>
       <c r="O7" s="130"/>
     </row>
-    <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="J8" s="165" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5244,7 +5227,7 @@
       <c r="N8" s="12"/>
       <c r="O8" s="130"/>
     </row>
-    <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -5258,16 +5241,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L9" s="92"/>
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="130"/>
     </row>
-    <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -5279,27 +5262,27 @@
         <v>0</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L10" s="92"/>
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="130"/>
     </row>
-    <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J11" s="165" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L11" s="92"/>
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
       <c r="O11" s="130"/>
     </row>
-    <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5338,13 +5321,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="219"/>
-      <c r="B15" s="220" t="s">
+    <row r="15" spans="1:20" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="237"/>
+      <c r="B15" s="238" t="s">
         <v>49</v>
       </c>
-      <c r="C15" s="221"/>
-      <c r="D15" s="221"/>
+      <c r="C15" s="239"/>
+      <c r="D15" s="239"/>
       <c r="E15" s="18"/>
       <c r="F15" s="153"/>
       <c r="G15" s="153"/>
@@ -5364,13 +5347,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="219"/>
-      <c r="B16" s="222" t="s">
+    <row r="16" spans="1:20" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="237"/>
+      <c r="B16" s="240" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="239"/>
       <c r="E16" s="18"/>
       <c r="F16" s="153"/>
       <c r="G16" s="153"/>
@@ -5388,12 +5371,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="222" t="s">
+    <row r="17" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="240" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="221"/>
-      <c r="D17" s="221"/>
+      <c r="C17" s="239"/>
+      <c r="D17" s="239"/>
       <c r="E17" s="18"/>
       <c r="F17" s="153"/>
       <c r="G17" s="153"/>
@@ -5409,12 +5392,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="230" t="s">
+    <row r="18" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="244" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="221"/>
-      <c r="D18" s="221"/>
+      <c r="C18" s="239"/>
+      <c r="D18" s="239"/>
       <c r="E18" s="18"/>
       <c r="F18" s="153"/>
       <c r="G18" s="153"/>
@@ -5430,12 +5413,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="226" t="s">
+    <row r="19" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="235" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="227"/>
-      <c r="D19" s="227"/>
+      <c r="C19" s="236"/>
+      <c r="D19" s="236"/>
       <c r="E19" s="20"/>
       <c r="F19" s="153"/>
       <c r="G19" s="153"/>
@@ -5451,12 +5434,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="222" t="s">
+    <row r="20" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="240" t="s">
         <v>61</v>
       </c>
-      <c r="C20" s="221"/>
-      <c r="D20" s="221"/>
+      <c r="C20" s="239"/>
+      <c r="D20" s="239"/>
       <c r="E20" s="18"/>
       <c r="F20" s="153"/>
       <c r="G20" s="153"/>
@@ -5472,7 +5455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="69" t="s">
         <v>52</v>
       </c>
@@ -5494,12 +5477,12 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="231" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="232"/>
-      <c r="D22" s="232"/>
-      <c r="E22" s="232"/>
+      <c r="B22" s="245" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="246"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="246"/>
       <c r="F22" s="153"/>
       <c r="G22" s="153"/>
       <c r="H22" s="153"/>
@@ -5516,7 +5499,7 @@
     </row>
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M23" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O23" s="1">
         <f>MAX(J3:J11)</f>
@@ -5546,7 +5529,7 @@
       <c r="H25" s="26"/>
       <c r="M25" s="24"/>
       <c r="N25" s="24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="O25" s="27">
         <f>IFERROR(ROUND(O24/O23,3),0)</f>
@@ -5638,6 +5621,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B22:E22"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="A15:A16"/>
@@ -5646,11 +5634,6 @@
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="84" orientation="landscape" r:id="rId1"/>
@@ -5670,33 +5653,33 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:U66"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="11" width="7.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.1328125" style="1"/>
-    <col min="15" max="15" width="14.06640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="11" width="7.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.6328125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.08984375" style="1"/>
+    <col min="15" max="15" width="14.08984375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:21" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S2" s="10"/>
       <c r="T2" s="11"/>
@@ -5704,7 +5687,7 @@
     </row>
     <row r="3" spans="1:21" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J3" s="165" t="str">
         <f>IF(L3&lt;&gt;0,J2+1,"0")</f>
@@ -5713,13 +5696,13 @@
       <c r="K3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="175"/>
-      <c r="M3" s="175"/>
-      <c r="N3" s="175"/>
-      <c r="O3" s="175"/>
+      <c r="L3" s="177"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S3" s="10"/>
       <c r="T3" s="11"/>
@@ -5747,7 +5730,7 @@
       <c r="O4" s="174"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S4" s="10"/>
       <c r="T4" s="11"/>
@@ -5770,9 +5753,9 @@
         <v>2</v>
       </c>
       <c r="L5" s="174"/>
-      <c r="M5" s="180"/>
-      <c r="N5" s="180"/>
-      <c r="O5" s="180"/>
+      <c r="M5" s="175"/>
+      <c r="N5" s="175"/>
+      <c r="O5" s="175"/>
       <c r="Q5" s="9"/>
       <c r="R5" s="13" t="s">
         <v>12</v>
@@ -5798,13 +5781,13 @@
         <v>3</v>
       </c>
       <c r="L6" s="174"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="180"/>
-      <c r="O6" s="180"/>
-    </row>
-    <row r="7" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="175"/>
+      <c r="N6" s="175"/>
+      <c r="O6" s="175"/>
+    </row>
+    <row r="7" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -5819,19 +5802,19 @@
         <v>4</v>
       </c>
       <c r="L7" s="174"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-    </row>
-    <row r="8" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M7" s="175"/>
+      <c r="N7" s="175"/>
+      <c r="O7" s="175"/>
+    </row>
+    <row r="8" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="J8" s="165" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -5840,11 +5823,11 @@
         <v>5</v>
       </c>
       <c r="L8" s="174"/>
-      <c r="M8" s="180"/>
-      <c r="N8" s="180"/>
-      <c r="O8" s="180"/>
-    </row>
-    <row r="9" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M8" s="175"/>
+      <c r="N8" s="175"/>
+      <c r="O8" s="175"/>
+    </row>
+    <row r="9" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -5858,16 +5841,16 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="L9" s="174"/>
-      <c r="M9" s="180"/>
-      <c r="N9" s="180"/>
-      <c r="O9" s="180"/>
-    </row>
-    <row r="10" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M9" s="175"/>
+      <c r="N9" s="175"/>
+      <c r="O9" s="175"/>
+    </row>
+    <row r="10" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -5879,30 +5862,30 @@
         <v>0</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L10" s="174"/>
-      <c r="M10" s="180"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="180"/>
-    </row>
-    <row r="11" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M10" s="175"/>
+      <c r="N10" s="175"/>
+      <c r="O10" s="175"/>
+    </row>
+    <row r="11" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J11" s="165" t="str">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L11" s="174"/>
-      <c r="M11" s="180"/>
-      <c r="N11" s="180"/>
-      <c r="O11" s="180"/>
-    </row>
-    <row r="12" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M11" s="175"/>
+      <c r="N11" s="175"/>
+      <c r="O11" s="175"/>
+    </row>
+    <row r="12" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
     </row>
-    <row r="13" spans="1:21" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -5945,13 +5928,13 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="219"/>
-      <c r="B16" s="220" t="s">
+    <row r="16" spans="1:21" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="237"/>
+      <c r="B16" s="238" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="221"/>
-      <c r="D16" s="221"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="239"/>
       <c r="E16" s="18"/>
       <c r="F16" s="153"/>
       <c r="G16" s="153"/>
@@ -5967,13 +5950,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="219"/>
-      <c r="B17" s="222" t="s">
+    <row r="17" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="237"/>
+      <c r="B17" s="240" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="221"/>
-      <c r="D17" s="221"/>
+      <c r="C17" s="239"/>
+      <c r="D17" s="239"/>
       <c r="E17" s="18"/>
       <c r="F17" s="153"/>
       <c r="G17" s="153"/>
@@ -5989,12 +5972,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="222" t="s">
+    <row r="18" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="240" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="221"/>
-      <c r="D18" s="221"/>
+      <c r="C18" s="239"/>
+      <c r="D18" s="239"/>
       <c r="E18" s="18"/>
       <c r="F18" s="153"/>
       <c r="G18" s="153"/>
@@ -6010,12 +5993,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="230" t="s">
+    <row r="19" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="244" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="221"/>
-      <c r="D19" s="221"/>
+      <c r="C19" s="239"/>
+      <c r="D19" s="239"/>
       <c r="E19" s="18"/>
       <c r="F19" s="153"/>
       <c r="G19" s="153"/>
@@ -6031,13 +6014,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="222" t="s">
-        <v>133</v>
-      </c>
-      <c r="C20" s="221"/>
-      <c r="D20" s="221"/>
-      <c r="E20" s="233"/>
+    <row r="20" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="240" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="239"/>
+      <c r="D20" s="239"/>
+      <c r="E20" s="247"/>
       <c r="F20" s="153"/>
       <c r="G20" s="153"/>
       <c r="H20" s="153"/>
@@ -6052,12 +6035,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="222" t="s">
+    <row r="21" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="240" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="221"/>
-      <c r="D21" s="221"/>
+      <c r="C21" s="239"/>
+      <c r="D21" s="239"/>
       <c r="E21" s="18"/>
       <c r="F21" s="153"/>
       <c r="G21" s="153"/>
@@ -6073,13 +6056,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="223" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="224"/>
-      <c r="D22" s="224"/>
-      <c r="E22" s="225"/>
+    <row r="22" spans="1:15" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="241" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="242"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="243"/>
       <c r="F22" s="153"/>
       <c r="G22" s="153"/>
       <c r="H22" s="153"/>
@@ -6097,7 +6080,7 @@
     <row r="23" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L23" s="21"/>
       <c r="M23" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O23" s="1">
         <f>MAX(J3:J11)</f>
@@ -6242,6 +6225,20 @@
     <row r="66" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C9:F9"/>
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="L3:O3"/>
     <mergeCell ref="L9:O9"/>
@@ -6250,20 +6247,6 @@
     <mergeCell ref="L5:O5"/>
     <mergeCell ref="L6:O6"/>
     <mergeCell ref="L7:O7"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:E20"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" scale="79" orientation="landscape" r:id="rId1"/>
@@ -6286,30 +6269,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.73046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -6317,11 +6300,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -6338,7 +6321,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -6374,9 +6357,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -6386,29 +6369,29 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="175"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="177"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="177"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="179"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I8" s="174"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="181"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="176"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -6421,13 +6404,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="174"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="181"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="176"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -6438,54 +6421,54 @@
         <v>3</v>
       </c>
       <c r="I10" s="174"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="181"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="176"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I11" s="174"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="181"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="176"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I12" s="174"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="180"/>
-      <c r="L12" s="181"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
+      <c r="L12" s="176"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
+      <c r="L13" s="176"/>
+    </row>
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="174"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="175"/>
+      <c r="L14" s="176"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I13" s="174"/>
-      <c r="J13" s="180"/>
-      <c r="K13" s="180"/>
-      <c r="L13" s="181"/>
-    </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H14" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="174"/>
-      <c r="J14" s="180"/>
-      <c r="K14" s="180"/>
-      <c r="L14" s="181"/>
-    </row>
-    <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H15" s="12" t="s">
-        <v>146</v>
-      </c>
       <c r="I15" s="174"/>
-      <c r="J15" s="180"/>
-      <c r="K15" s="180"/>
-      <c r="L15" s="181"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
+      <c r="L15" s="176"/>
     </row>
     <row r="16" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H16" s="3"/>
@@ -6494,7 +6477,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
         <v>48</v>
       </c>
@@ -6535,24 +6518,24 @@
       <c r="K20" s="131"/>
       <c r="L20" s="132"/>
     </row>
-    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G22" s="26"/>
       <c r="H22" s="122" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I22" s="78"/>
       <c r="K22" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="110" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="69"/>
       <c r="D23" s="83"/>
@@ -6571,7 +6554,7 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="110" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="69"/>
       <c r="D24" s="83"/>
@@ -6590,7 +6573,7 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="69"/>
       <c r="D25" s="83"/>
@@ -6607,9 +6590,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="70"/>
       <c r="D26" s="70"/>
@@ -6624,9 +6607,9 @@
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G27" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
@@ -6641,7 +6624,7 @@
     </row>
     <row r="28" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -6658,13 +6641,13 @@
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="70"/>
       <c r="D30" s="83"/>
       <c r="E30" s="154"/>
       <c r="F30" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G30" s="83"/>
       <c r="H30" s="85">
@@ -6715,7 +6698,7 @@
     </row>
     <row r="35" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G35" s="94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -6731,7 +6714,7 @@
     <row r="36" spans="1:12" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I37" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J37" s="98"/>
       <c r="K37" s="98"/>
@@ -6800,30 +6783,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.33203125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.36328125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="6.265625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="6.26953125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -6831,11 +6814,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -6852,7 +6835,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -6888,9 +6871,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -6900,29 +6883,29 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="175"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="177"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="177"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="179"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I8" s="174"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="181"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="176"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -6935,13 +6918,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="174"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="181"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="176"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -6952,20 +6935,20 @@
         <v>3</v>
       </c>
       <c r="I10" s="174"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="181"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="176"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I11" s="174"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="181"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="176"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
@@ -6974,27 +6957,27 @@
       <c r="K12" s="12"/>
       <c r="L12" s="130"/>
     </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I13" s="92"/>
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
       <c r="L13" s="130"/>
     </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H14" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I14" s="92"/>
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
       <c r="L14" s="130"/>
     </row>
-    <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H15" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I15" s="92"/>
       <c r="J15" s="12"/>
@@ -7008,7 +6991,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
         <v>48</v>
       </c>
@@ -7025,32 +7008,32 @@
       <c r="L17" s="76"/>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="234"/>
-      <c r="B18" s="235"/>
-      <c r="C18" s="235"/>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="236"/>
+      <c r="A18" s="248"/>
+      <c r="B18" s="249"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="250"/>
     </row>
     <row r="19" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="237"/>
-      <c r="B19" s="238"/>
-      <c r="C19" s="238"/>
-      <c r="D19" s="238"/>
-      <c r="E19" s="238"/>
-      <c r="F19" s="238"/>
-      <c r="G19" s="238"/>
-      <c r="H19" s="238"/>
-      <c r="I19" s="238"/>
-      <c r="J19" s="238"/>
-      <c r="K19" s="238"/>
-      <c r="L19" s="239"/>
+      <c r="A19" s="251"/>
+      <c r="B19" s="252"/>
+      <c r="C19" s="252"/>
+      <c r="D19" s="252"/>
+      <c r="E19" s="252"/>
+      <c r="F19" s="252"/>
+      <c r="G19" s="252"/>
+      <c r="H19" s="252"/>
+      <c r="I19" s="252"/>
+      <c r="J19" s="252"/>
+      <c r="K19" s="252"/>
+      <c r="L19" s="253"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="129" t="s">
@@ -7068,24 +7051,24 @@
       <c r="K20" s="131"/>
       <c r="L20" s="132"/>
     </row>
-    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G22" s="26"/>
       <c r="H22" s="122" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I22" s="78"/>
       <c r="K22" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="110" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="69"/>
       <c r="D23" s="83"/>
@@ -7107,7 +7090,7 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="110" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="69"/>
       <c r="D24" s="83"/>
@@ -7129,7 +7112,7 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="69"/>
       <c r="D25" s="83"/>
@@ -7149,9 +7132,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="70"/>
       <c r="D26" s="70"/>
@@ -7166,9 +7149,9 @@
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
     </row>
-    <row r="27" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:12" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G27" s="94" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
@@ -7183,7 +7166,7 @@
     </row>
     <row r="28" spans="1:12" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7200,7 +7183,7 @@
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="70"/>
       <c r="D30" s="83"/>
@@ -7210,7 +7193,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G30" s="83"/>
       <c r="H30" s="85">
@@ -7264,7 +7247,7 @@
     </row>
     <row r="35" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G35" s="94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="10"/>
@@ -7280,7 +7263,7 @@
     <row r="36" spans="1:12" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I37" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J37" s="98"/>
       <c r="K37" s="98"/>
@@ -7316,17 +7299,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A18:L19"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I10:L10"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="I8:L8"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="I9:L9"/>
     <mergeCell ref="C9:F9"/>
+    <mergeCell ref="A18:L19"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I10:L10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
@@ -7346,30 +7329,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.59765625" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.6328125" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="7.19921875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -7377,11 +7360,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -7398,7 +7381,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -7434,9 +7417,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -7446,29 +7429,29 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="175"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="177"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="177"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="179"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I8" s="174"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="181"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="176"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -7481,13 +7464,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="174"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="181"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="176"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -7498,54 +7481,54 @@
         <v>3</v>
       </c>
       <c r="I10" s="174"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="181"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="176"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I11" s="174"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="181"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="176"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I12" s="174"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="180"/>
-      <c r="L12" s="181"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
+      <c r="L12" s="176"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H13" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="I13" s="174"/>
+      <c r="J13" s="175"/>
+      <c r="K13" s="175"/>
+      <c r="L13" s="176"/>
+    </row>
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H14" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="I14" s="174"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="175"/>
+      <c r="L14" s="176"/>
+    </row>
+    <row r="15" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H15" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="I13" s="174"/>
-      <c r="J13" s="180"/>
-      <c r="K13" s="180"/>
-      <c r="L13" s="181"/>
-    </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H14" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="174"/>
-      <c r="J14" s="180"/>
-      <c r="K14" s="180"/>
-      <c r="L14" s="181"/>
-    </row>
-    <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H15" s="12" t="s">
-        <v>146</v>
-      </c>
       <c r="I15" s="174"/>
-      <c r="J15" s="180"/>
-      <c r="K15" s="180"/>
-      <c r="L15" s="181"/>
+      <c r="J15" s="175"/>
+      <c r="K15" s="175"/>
+      <c r="L15" s="176"/>
     </row>
     <row r="16" spans="1:12" ht="9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H16" s="3"/>
@@ -7554,7 +7537,7 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
         <v>48</v>
       </c>
@@ -7571,32 +7554,32 @@
       <c r="L17" s="76"/>
     </row>
     <row r="18" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="234"/>
-      <c r="B18" s="235"/>
-      <c r="C18" s="235"/>
-      <c r="D18" s="235"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="235"/>
-      <c r="G18" s="235"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="235"/>
-      <c r="J18" s="235"/>
-      <c r="K18" s="235"/>
-      <c r="L18" s="236"/>
+      <c r="A18" s="248"/>
+      <c r="B18" s="249"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
+      <c r="K18" s="249"/>
+      <c r="L18" s="250"/>
     </row>
     <row r="19" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="237"/>
-      <c r="B19" s="238"/>
-      <c r="C19" s="238"/>
-      <c r="D19" s="238"/>
-      <c r="E19" s="238"/>
-      <c r="F19" s="238"/>
-      <c r="G19" s="238"/>
-      <c r="H19" s="238"/>
-      <c r="I19" s="238"/>
-      <c r="J19" s="238"/>
-      <c r="K19" s="238"/>
-      <c r="L19" s="239"/>
+      <c r="A19" s="251"/>
+      <c r="B19" s="252"/>
+      <c r="C19" s="252"/>
+      <c r="D19" s="252"/>
+      <c r="E19" s="252"/>
+      <c r="F19" s="252"/>
+      <c r="G19" s="252"/>
+      <c r="H19" s="252"/>
+      <c r="I19" s="252"/>
+      <c r="J19" s="252"/>
+      <c r="K19" s="252"/>
+      <c r="L19" s="253"/>
     </row>
     <row r="20" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="129" t="s">
@@ -7626,24 +7609,24 @@
       <c r="K20" s="131"/>
       <c r="L20" s="132"/>
     </row>
-    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G22" s="26"/>
       <c r="H22" s="109" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I22" s="78"/>
       <c r="K22" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="110" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C23" s="69"/>
       <c r="D23" s="83"/>
@@ -7669,7 +7652,7 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="110" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="69"/>
       <c r="D24" s="83"/>
@@ -7695,7 +7678,7 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="110" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="69"/>
       <c r="D25" s="83"/>
@@ -7719,9 +7702,9 @@
       </c>
       <c r="L25" s="21"/>
     </row>
-    <row r="26" spans="1:12" ht="12.75" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="69" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" s="70"/>
       <c r="D26" s="70"/>
@@ -7744,7 +7727,7 @@
       <c r="E27" s="114"/>
       <c r="F27" s="114"/>
       <c r="G27" s="116" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" s="117"/>
       <c r="I27" s="117"/>
@@ -7772,7 +7755,7 @@
     </row>
     <row r="29" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -7789,7 +7772,7 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="70"/>
       <c r="D31" s="83"/>
@@ -7799,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="69" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G31" s="83"/>
       <c r="H31" s="85">
@@ -7853,7 +7836,7 @@
     </row>
     <row r="36" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="G36" s="94" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
@@ -7869,7 +7852,7 @@
     <row r="37" spans="1:12" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="38" spans="1:12" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I38" s="71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J38" s="98"/>
       <c r="K38" s="98"/>
@@ -7929,30 +7912,30 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M29"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="12.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.86328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1328125" style="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="1" customWidth="1"/>
-    <col min="5" max="7" width="7.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="7.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.08984375" style="1"/>
+    <col min="3" max="3" width="12.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.7265625" style="1" customWidth="1"/>
+    <col min="5" max="7" width="7.26953125" style="1" customWidth="1"/>
     <col min="8" max="8" width="7" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="4.73046875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.265625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.265625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1328125" style="1"/>
+    <col min="9" max="9" width="7.26953125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.26953125" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:12" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J2" s="10"/>
       <c r="K2" s="11"/>
@@ -7960,11 +7943,11 @@
     </row>
     <row r="3" spans="1:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J3" s="10"/>
       <c r="K3" s="11"/>
@@ -7981,7 +7964,7 @@
       <c r="F4" s="8"/>
       <c r="H4" s="9"/>
       <c r="I4" s="13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" s="10"/>
       <c r="K4" s="11"/>
@@ -8017,9 +8000,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="92"/>
@@ -8029,29 +8012,29 @@
       <c r="H7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="I7" s="175"/>
-      <c r="J7" s="176"/>
-      <c r="K7" s="176"/>
-      <c r="L7" s="177"/>
-    </row>
-    <row r="8" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="177"/>
+      <c r="J7" s="178"/>
+      <c r="K7" s="178"/>
+      <c r="L7" s="179"/>
+    </row>
+    <row r="8" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="175"/>
+      <c r="C8" s="177"/>
+      <c r="D8" s="177"/>
+      <c r="E8" s="177"/>
+      <c r="F8" s="177"/>
       <c r="H8" s="12" t="s">
         <v>1</v>
       </c>
       <c r="I8" s="174"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="180"/>
-      <c r="L8" s="181"/>
-    </row>
-    <row r="9" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="175"/>
+      <c r="K8" s="175"/>
+      <c r="L8" s="176"/>
+    </row>
+    <row r="9" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>16</v>
       </c>
@@ -8064,13 +8047,13 @@
         <v>2</v>
       </c>
       <c r="I9" s="174"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="180"/>
-      <c r="L9" s="181"/>
-    </row>
-    <row r="10" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="175"/>
+      <c r="K9" s="175"/>
+      <c r="L9" s="176"/>
+    </row>
+    <row r="10" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="174"/>
@@ -8081,53 +8064,53 @@
         <v>3</v>
       </c>
       <c r="I10" s="174"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180"/>
-      <c r="L10" s="181"/>
-    </row>
-    <row r="11" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="175"/>
+      <c r="K10" s="175"/>
+      <c r="L10" s="176"/>
+    </row>
+    <row r="11" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H11" s="12" t="s">
         <v>4</v>
       </c>
       <c r="I11" s="174"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="180"/>
-      <c r="L11" s="181"/>
-    </row>
-    <row r="12" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J11" s="175"/>
+      <c r="K11" s="175"/>
+      <c r="L11" s="176"/>
+    </row>
+    <row r="12" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="14"/>
       <c r="H12" s="12" t="s">
         <v>5</v>
       </c>
       <c r="I12" s="174"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="180"/>
-      <c r="L12" s="181"/>
-    </row>
-    <row r="13" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J12" s="175"/>
+      <c r="K12" s="175"/>
+      <c r="L12" s="176"/>
+    </row>
+    <row r="13" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="14"/>
       <c r="H13" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I13" s="174"/>
       <c r="J13" s="174"/>
       <c r="K13" s="174"/>
       <c r="L13" s="174"/>
     </row>
-    <row r="14" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="14"/>
       <c r="H14" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I14" s="174"/>
       <c r="J14" s="174"/>
       <c r="K14" s="174"/>
       <c r="L14" s="174"/>
     </row>
-    <row r="15" spans="1:12" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="17.149999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="14"/>
       <c r="H15" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="I15" s="174"/>
       <c r="J15" s="174"/>
@@ -8136,25 +8119,25 @@
     </row>
     <row r="16" spans="1:12" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="K16" s="164" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="171" t="s">
+        <v>151</v>
+      </c>
+      <c r="B17" s="190" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="191"/>
+      <c r="D17" s="191"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="191"/>
+      <c r="G17" s="191"/>
+      <c r="H17" s="191"/>
+      <c r="I17" s="192"/>
+      <c r="J17" s="168" t="s">
         <v>153</v>
-      </c>
-      <c r="B17" s="240" t="s">
-        <v>154</v>
-      </c>
-      <c r="C17" s="241"/>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="168" t="s">
-        <v>155</v>
       </c>
       <c r="K17" s="172"/>
       <c r="L17" s="173">
@@ -8163,21 +8146,21 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="243" t="s">
+      <c r="A18" s="180" t="s">
+        <v>162</v>
+      </c>
+      <c r="B18" s="182" t="s">
+        <v>160</v>
+      </c>
+      <c r="C18" s="183"/>
+      <c r="D18" s="183"/>
+      <c r="E18" s="183"/>
+      <c r="F18" s="183"/>
+      <c r="G18" s="183"/>
+      <c r="H18" s="183"/>
+      <c r="I18" s="183"/>
+      <c r="J18" s="100" t="s">
         <v>164</v>
-      </c>
-      <c r="B18" s="246" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="247"/>
-      <c r="D18" s="247"/>
-      <c r="E18" s="247"/>
-      <c r="F18" s="247"/>
-      <c r="G18" s="247"/>
-      <c r="H18" s="247"/>
-      <c r="I18" s="247"/>
-      <c r="J18" s="100" t="s">
-        <v>166</v>
       </c>
       <c r="K18" s="156"/>
       <c r="L18" s="101">
@@ -8187,19 +8170,19 @@
       <c r="M18" s="102"/>
     </row>
     <row r="19" spans="1:13" ht="83.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="244"/>
-      <c r="B19" s="246" t="s">
-        <v>163</v>
-      </c>
-      <c r="C19" s="247"/>
-      <c r="D19" s="247"/>
-      <c r="E19" s="247"/>
-      <c r="F19" s="247"/>
-      <c r="G19" s="247"/>
-      <c r="H19" s="247"/>
-      <c r="I19" s="247"/>
+      <c r="A19" s="193"/>
+      <c r="B19" s="182" t="s">
+        <v>161</v>
+      </c>
+      <c r="C19" s="183"/>
+      <c r="D19" s="183"/>
+      <c r="E19" s="183"/>
+      <c r="F19" s="183"/>
+      <c r="G19" s="183"/>
+      <c r="H19" s="183"/>
+      <c r="I19" s="183"/>
       <c r="J19" s="103" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K19" s="157"/>
       <c r="L19" s="104">
@@ -8209,21 +8192,21 @@
       <c r="M19" s="102"/>
     </row>
     <row r="20" spans="1:13" ht="58.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="243" t="s">
+      <c r="A20" s="180" t="s">
+        <v>163</v>
+      </c>
+      <c r="B20" s="184" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="185"/>
+      <c r="D20" s="185"/>
+      <c r="E20" s="185"/>
+      <c r="F20" s="185"/>
+      <c r="G20" s="185"/>
+      <c r="H20" s="185"/>
+      <c r="I20" s="186"/>
+      <c r="J20" s="100" t="s">
         <v>165</v>
-      </c>
-      <c r="B20" s="248" t="s">
-        <v>156</v>
-      </c>
-      <c r="C20" s="249"/>
-      <c r="D20" s="249"/>
-      <c r="E20" s="249"/>
-      <c r="F20" s="249"/>
-      <c r="G20" s="249"/>
-      <c r="H20" s="249"/>
-      <c r="I20" s="250"/>
-      <c r="J20" s="100" t="s">
-        <v>167</v>
       </c>
       <c r="K20" s="158"/>
       <c r="L20" s="105">
@@ -8233,19 +8216,19 @@
       <c r="M20" s="102"/>
     </row>
     <row r="21" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="245"/>
-      <c r="B21" s="251" t="s">
-        <v>157</v>
-      </c>
-      <c r="C21" s="252"/>
-      <c r="D21" s="252"/>
-      <c r="E21" s="252"/>
-      <c r="F21" s="252"/>
-      <c r="G21" s="252"/>
-      <c r="H21" s="252"/>
-      <c r="I21" s="253"/>
+      <c r="A21" s="181"/>
+      <c r="B21" s="187" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="188"/>
+      <c r="D21" s="188"/>
+      <c r="E21" s="188"/>
+      <c r="F21" s="188"/>
+      <c r="G21" s="188"/>
+      <c r="H21" s="188"/>
+      <c r="I21" s="189"/>
       <c r="J21" s="106" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K21" s="159"/>
       <c r="L21" s="107">
@@ -8268,7 +8251,7 @@
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="83"/>
       <c r="D24" s="70"/>
@@ -8284,9 +8267,9 @@
     <row r="25" spans="1:13" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="L25" s="90"/>
     </row>
-    <row r="26" spans="1:13" ht="13.9" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" ht="14" thickBot="1" x14ac:dyDescent="0.35">
       <c r="I26" s="71" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J26" s="98"/>
       <c r="K26" s="98"/>
@@ -8313,6 +8296,16 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="B18:I18"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B21:I21"/>
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="I7:L7"/>
@@ -8324,16 +8317,6 @@
     <mergeCell ref="I10:L10"/>
     <mergeCell ref="I11:L11"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.15748031496062992" top="0.98425196850393704" bottom="0.39370078740157483" header="0.43307086614173229" footer="0.19685039370078741"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -8347,12 +8330,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <documentManagement>
+    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8422,18 +8405,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <documentManagement>
-    <PublishingExpirationDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <PublishingStartDate xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A807C1-6DB8-4C6A-8DCB-8B5F61EFE299}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64838F1D-7ECA-4F32-944F-43492487C498}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8456,16 +8446,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64838F1D-7ECA-4F32-944F-43492487C498}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A807C1-6DB8-4C6A-8DCB-8B5F61EFE299}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>